--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\incoming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4162638A-A566-4C2E-A4EC-5B98CBC03261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26B9D1A-AF2C-4916-87A8-D1094F7BEF14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -181,7 +181,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="_-&quot;¥&quot;* #,##0.00_-\ ;\-&quot;¥&quot;* #,##0.00_-\ ;_-&quot;¥&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -284,7 +284,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -299,16 +299,16 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1249,392 +1249,183 @@
       <c r="E31" s="5"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A32" s="4">
-        <v>45901</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C32" s="1">
-        <v>461395</v>
-      </c>
+      <c r="A32" s="4"/>
+      <c r="B32" s="5"/>
       <c r="D32" s="7"/>
       <c r="E32" s="5"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A33" s="4">
-        <v>45902</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C33" s="1">
-        <v>428348</v>
-      </c>
+      <c r="A33" s="4"/>
+      <c r="B33" s="5"/>
       <c r="D33" s="7"/>
       <c r="E33" s="5"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A34" s="4">
-        <v>45903</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C34" s="1">
-        <v>632743</v>
-      </c>
+      <c r="A34" s="4"/>
+      <c r="B34" s="5"/>
       <c r="D34" s="7"/>
       <c r="E34" s="5"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A35" s="4">
-        <v>45904</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" s="1">
-        <v>418060</v>
-      </c>
+      <c r="A35" s="4"/>
+      <c r="B35" s="5"/>
       <c r="D35" s="7"/>
       <c r="E35" s="5"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A36" s="4">
-        <v>45905</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C36" s="1">
-        <v>365377</v>
-      </c>
+      <c r="A36" s="4"/>
+      <c r="B36" s="5"/>
       <c r="D36" s="7"/>
       <c r="E36" s="5"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A37" s="4">
-        <v>45906</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C37" s="1">
-        <v>942536</v>
-      </c>
+      <c r="A37" s="4"/>
+      <c r="B37" s="5"/>
       <c r="D37" s="7"/>
       <c r="E37" s="5"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A38" s="4">
-        <v>45907</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C38" s="1">
-        <v>930983</v>
-      </c>
+      <c r="A38" s="4"/>
+      <c r="B38" s="5"/>
       <c r="D38" s="7"/>
       <c r="E38" s="5"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A39" s="4">
-        <v>45908</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C39" s="1">
-        <v>495802</v>
-      </c>
+      <c r="A39" s="4"/>
+      <c r="B39" s="5"/>
       <c r="D39" s="7"/>
       <c r="E39" s="5"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A40" s="4">
-        <v>45909</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C40" s="1">
-        <v>489821</v>
-      </c>
+      <c r="A40" s="4"/>
+      <c r="B40" s="5"/>
       <c r="D40" s="7"/>
       <c r="E40" s="5"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A41" s="4">
-        <v>45910</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C41" s="1">
-        <v>624958</v>
-      </c>
+      <c r="A41" s="4"/>
+      <c r="B41" s="5"/>
       <c r="D41" s="7"/>
       <c r="E41" s="5"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A42" s="4">
-        <v>45911</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C42" s="1">
-        <v>641925</v>
-      </c>
+      <c r="A42" s="4"/>
+      <c r="B42" s="5"/>
       <c r="D42" s="7"/>
       <c r="E42" s="5"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A43" s="4">
-        <v>45912</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C43" s="1">
-        <v>654224</v>
-      </c>
+      <c r="A43" s="4"/>
+      <c r="B43" s="5"/>
       <c r="D43" s="7"/>
       <c r="E43" s="5"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A44" s="4">
-        <v>45913</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C44" s="1">
-        <v>1010713</v>
-      </c>
+      <c r="A44" s="4"/>
+      <c r="B44" s="5"/>
       <c r="D44" s="7"/>
       <c r="E44" s="5"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A45" s="4">
-        <v>45914</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C45" s="1">
-        <v>939842</v>
-      </c>
+      <c r="A45" s="4"/>
+      <c r="B45" s="5"/>
       <c r="D45" s="7"/>
       <c r="E45" s="5"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A46" s="4">
-        <v>45915</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C46" s="1">
-        <v>664766</v>
-      </c>
+      <c r="A46" s="4"/>
+      <c r="B46" s="5"/>
       <c r="D46" s="7"/>
       <c r="E46" s="5"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A47" s="4">
-        <v>45916</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C47" s="1">
-        <v>559368</v>
-      </c>
+      <c r="A47" s="4"/>
+      <c r="B47" s="5"/>
       <c r="D47" s="7"/>
       <c r="E47" s="5"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A48" s="4">
-        <v>45917</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C48" s="1">
-        <v>637114</v>
-      </c>
+      <c r="A48" s="4"/>
+      <c r="B48" s="5"/>
       <c r="D48" s="7"/>
       <c r="E48" s="5"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A49" s="4">
-        <v>45918</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C49" s="1">
-        <v>446759</v>
-      </c>
+      <c r="A49" s="4"/>
+      <c r="B49" s="5"/>
       <c r="D49" s="7"/>
       <c r="E49" s="5"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A50" s="4">
-        <v>45919</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C50" s="1">
-        <v>402255</v>
-      </c>
+      <c r="A50" s="4"/>
+      <c r="B50" s="5"/>
       <c r="D50" s="7"/>
       <c r="E50" s="5"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A51" s="4">
-        <v>45920</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C51" s="1">
-        <v>729354</v>
-      </c>
+      <c r="A51" s="4"/>
+      <c r="B51" s="5"/>
       <c r="D51" s="7"/>
       <c r="E51" s="5"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A52" s="4">
-        <v>45921</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C52" s="1">
-        <v>846332</v>
-      </c>
+      <c r="A52" s="4"/>
+      <c r="B52" s="5"/>
       <c r="D52" s="7"/>
       <c r="E52" s="5"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A53" s="4">
-        <v>45922</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C53" s="1">
-        <v>570403</v>
-      </c>
+      <c r="A53" s="4"/>
+      <c r="B53" s="5"/>
       <c r="D53" s="7"/>
       <c r="E53" s="5"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A54" s="4">
-        <v>45923</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C54" s="1">
-        <v>811024</v>
-      </c>
+      <c r="A54" s="4"/>
+      <c r="B54" s="5"/>
       <c r="D54" s="7"/>
       <c r="E54" s="5"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A55" s="4">
-        <v>45924</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C55" s="1">
-        <v>515426</v>
-      </c>
+      <c r="A55" s="4"/>
+      <c r="B55" s="5"/>
       <c r="D55" s="7"/>
       <c r="E55" s="5"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A56" s="4">
-        <v>45925</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C56" s="1">
-        <v>594833</v>
-      </c>
+      <c r="A56" s="4"/>
+      <c r="B56" s="5"/>
       <c r="D56" s="7"/>
       <c r="E56" s="5"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A57" s="4">
-        <v>45926</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C57" s="1">
-        <v>580727</v>
-      </c>
+      <c r="A57" s="4"/>
+      <c r="B57" s="5"/>
       <c r="D57" s="7"/>
       <c r="E57" s="5"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A58" s="4">
-        <v>45927</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C58" s="1">
-        <v>965438</v>
-      </c>
+      <c r="A58" s="4"/>
+      <c r="B58" s="5"/>
       <c r="D58" s="7"/>
       <c r="E58" s="5"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A59" s="4">
-        <v>45928</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C59" s="1">
-        <v>969264</v>
-      </c>
+      <c r="A59" s="4"/>
+      <c r="B59" s="5"/>
       <c r="D59" s="7"/>
       <c r="E59" s="5"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A60" s="4">
-        <v>45929</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C60" s="1">
-        <v>383738</v>
-      </c>
+      <c r="A60" s="4"/>
+      <c r="B60" s="5"/>
       <c r="D60" s="7"/>
       <c r="E60" s="5"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A61" s="4">
-        <v>45930</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C61" s="6">
-        <v>616027</v>
-      </c>
+      <c r="A61" s="4"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="6"/>
       <c r="D61" s="7"/>
       <c r="E61" s="5"/>
     </row>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1721</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1722</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1768" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,11 +208,17 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -223,31 +229,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -261,18 +252,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -284,7 +268,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -292,6 +283,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -313,21 +311,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -336,8 +319,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -351,9 +343,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,121 +482,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,7 +500,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,31 +542,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,23 +586,26 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -648,24 +651,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -680,6 +665,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,9 +838,9 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
@@ -849,10 +849,10 @@
     <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1722"/>
+  <dimension ref="A1:E1723"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23097,8 +23097,19 @@
         <v>737483</v>
       </c>
     </row>
+    <row r="1723" customHeight="1" spans="1:3">
+      <c r="A1723" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1723" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1723" s="2">
+        <v>747392</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1721">
+  <autoFilter ref="A1:E1722">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1722</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1723</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -209,7 +209,73 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -222,13 +288,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -237,8 +296,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -253,69 +328,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -335,25 +351,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +410,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,25 +440,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,19 +500,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,7 +524,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,97 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,33 +583,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -621,6 +594,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -640,17 +622,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -662,6 +633,15 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -680,6 +660,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,9 +838,9 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
@@ -849,10 +849,10 @@
     <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1723"/>
+  <dimension ref="A1:E1724"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23108,8 +23108,19 @@
         <v>747392</v>
       </c>
     </row>
+    <row r="1724" customHeight="1" spans="1:3">
+      <c r="A1724" s="1">
+        <v>46284</v>
+      </c>
+      <c r="B1724" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1724" s="2">
+        <v>894007</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1722">
+  <autoFilter ref="A1:E1723">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1723</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1724</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -215,11 +215,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -232,9 +238,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -245,8 +251,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -260,7 +290,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -274,17 +312,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -298,62 +346,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,19 +374,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,13 +494,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,25 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,55 +524,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,43 +548,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,6 +583,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -594,15 +603,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -622,6 +622,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -633,15 +642,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,145 +688,145 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -838,9 +838,9 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
@@ -849,10 +849,10 @@
     <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1724"/>
+  <dimension ref="A1:E1725"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23119,8 +23119,19 @@
         <v>894007</v>
       </c>
     </row>
+    <row r="1725" customHeight="1" spans="1:3">
+      <c r="A1725" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B1725" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1725" s="2">
+        <v>614147</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1723">
+  <autoFilter ref="A1:E1724">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1724</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1725</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
@@ -209,36 +209,22 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -252,7 +238,22 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -267,10 +268,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -290,23 +308,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -320,7 +322,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -338,15 +339,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,103 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,37 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,19 +542,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -585,8 +585,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -607,6 +609,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -618,15 +629,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -664,19 +666,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,9 +838,9 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
@@ -849,10 +849,10 @@
     <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1725"/>
+  <dimension ref="A1:E1726"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23130,8 +23130,19 @@
         <v>614147</v>
       </c>
     </row>
+    <row r="1726" customHeight="1" spans="1:3">
+      <c r="A1726" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1726" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1726" s="2">
+        <v>281473</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1724">
+  <autoFilter ref="A1:E1725">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1725</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1726</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -166,8 +166,8 @@
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
@@ -211,66 +211,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -292,9 +238,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -308,7 +260,68 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -322,8 +335,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -338,24 +352,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,7 +374,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +440,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,25 +452,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,13 +464,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,31 +512,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,61 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -554,7 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,17 +583,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -613,7 +602,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,17 +622,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -663,11 +657,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -676,7 +676,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1726"/>
+  <dimension ref="A1:E1727"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23141,8 +23141,19 @@
         <v>281473</v>
       </c>
     </row>
+    <row r="1727" customHeight="1" spans="1:3">
+      <c r="A1727" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1727" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1727" s="2">
+        <v>920943</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1725">
+  <autoFilter ref="A1:E1726">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1726</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1727</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -211,12 +211,27 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -224,22 +239,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -260,13 +268,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -274,23 +275,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -304,32 +289,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -352,10 +330,32 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,7 +374,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,19 +494,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,85 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,61 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -602,22 +602,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -636,8 +621,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -672,11 +657,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -839,14 +839,14 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
@@ -854,7 +854,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1727"/>
+  <dimension ref="A1:E1728"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23152,8 +23152,19 @@
         <v>920943</v>
       </c>
     </row>
+    <row r="1728" customHeight="1" spans="1:3">
+      <c r="A1728" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B1728" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1728" s="2">
+        <v>680640</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1726">
+  <autoFilter ref="A1:E1727">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1727</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1728</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,9 +164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -211,12 +211,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,36 +225,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -275,39 +251,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -330,7 +274,46 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -344,8 +327,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -354,6 +338,22 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +488,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,49 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,85 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,19 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -598,6 +598,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -614,6 +629,30 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -641,45 +680,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,9 +838,9 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
@@ -849,10 +849,10 @@
     <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1728"/>
+  <dimension ref="A1:E1729"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23163,8 +23163,19 @@
         <v>680640</v>
       </c>
     </row>
+    <row r="1729" customHeight="1" spans="1:3">
+      <c r="A1729" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B1729" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1729" s="2">
+        <v>624008</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1727">
+  <autoFilter ref="A1:E1728">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1728</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1729</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -216,7 +216,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -231,51 +231,6 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -298,7 +253,14 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -306,9 +268,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -317,6 +287,22 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -329,15 +315,15 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -353,7 +339,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -380,7 +380,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,19 +392,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,43 +422,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,19 +458,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,37 +482,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,19 +524,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -598,30 +598,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -636,8 +612,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,8 +636,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -680,6 +671,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,23 +838,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1729"/>
+  <dimension ref="A1:E1730"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23174,8 +23174,19 @@
         <v>624008</v>
       </c>
     </row>
+    <row r="1730" customHeight="1" spans="1:3">
+      <c r="A1730" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B1730" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1730" s="2">
+        <v>669376</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1728">
+  <autoFilter ref="A1:E1729">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1729</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1730</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -166,9 +166,9 @@
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -211,6 +211,105 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -222,15 +321,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -245,93 +345,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -342,20 +356,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,7 +374,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +494,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,55 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,97 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -598,26 +598,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -636,8 +616,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,6 +654,26 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,9 +838,9 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
@@ -849,10 +849,10 @@
     <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1730"/>
+  <dimension ref="A1:E1731"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23185,8 +23185,19 @@
         <v>669376</v>
       </c>
     </row>
+    <row r="1731" customHeight="1" spans="1:3">
+      <c r="A1731" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B1731" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1731" s="2">
+        <v>539069</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1729">
+  <autoFilter ref="A1:E1730">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1730</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1731</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -209,13 +209,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -224,7 +217,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,29 +241,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -267,32 +253,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -315,7 +285,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -329,6 +299,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -336,11 +307,41 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -351,11 +352,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -380,7 +380,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,13 +404,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,49 +440,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,13 +470,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,7 +482,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,55 +548,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,32 +583,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -622,17 +607,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -666,8 +651,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -675,8 +660,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -839,14 +839,14 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
@@ -854,7 +854,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1731"/>
+  <dimension ref="A1:E1732"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23196,8 +23196,19 @@
         <v>539069</v>
       </c>
     </row>
+    <row r="1732" customHeight="1" spans="1:3">
+      <c r="A1732" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B1732" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1732" s="2">
+        <v>1022537</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1730">
+  <autoFilter ref="A1:E1731">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1731</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1732</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,48 +208,11 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -268,9 +231,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -285,7 +262,36 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -300,17 +306,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -322,16 +321,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -346,14 +338,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,19 +374,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,31 +386,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,13 +422,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,7 +440,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,13 +464,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,67 +548,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -579,30 +579,6 @@
       </top>
       <bottom style="thin">
         <color indexed="22"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -637,6 +613,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -652,7 +652,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,23 +675,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,23 +838,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1732"/>
+  <dimension ref="A1:E1733"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23207,8 +23207,19 @@
         <v>1022537</v>
       </c>
     </row>
+    <row r="1733" customHeight="1" spans="1:3">
+      <c r="A1733" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B1733" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1733" s="2">
+        <v>323293</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1731">
+  <autoFilter ref="A1:E1732">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1732</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1733</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,7 +208,103 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -224,52 +320,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -283,69 +336,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -374,7 +374,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +404,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,25 +458,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,79 +500,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,37 +524,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,6 +583,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -594,6 +603,17 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -628,35 +648,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -668,6 +659,15 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,23 +838,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1733"/>
+  <dimension ref="A1:E1734"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23218,8 +23218,19 @@
         <v>323293</v>
       </c>
     </row>
+    <row r="1734" customHeight="1" spans="1:3">
+      <c r="A1734" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B1734" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1734" s="2">
+        <v>410623</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1732">
+  <autoFilter ref="A1:E1733">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1733</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1734</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -209,14 +209,36 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -232,30 +254,23 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -269,15 +284,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -290,37 +304,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -337,10 +328,18 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -352,8 +351,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,31 +482,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,103 +530,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,31 +548,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,15 +583,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -609,11 +600,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,17 +637,31 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -662,24 +680,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1734"/>
+  <dimension ref="A1:E1735"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23229,8 +23229,16 @@
         <v>410623</v>
       </c>
     </row>
+    <row r="1735" customHeight="1" spans="1:2">
+      <c r="A1735" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B1735" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1733">
+  <autoFilter ref="A1:E1734">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1735</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1736</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
@@ -208,6 +208,20 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -224,7 +238,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -237,9 +265,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -253,64 +296,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -329,10 +319,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -344,10 +343,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -374,96 +374,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -476,13 +386,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,7 +452,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,13 +494,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,19 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,13 +536,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -646,15 +646,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -666,6 +657,15 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,9 +838,9 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
@@ -849,10 +849,10 @@
     <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1736"/>
+  <dimension ref="A1:E1737"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23251,8 +23251,19 @@
         <v>336367</v>
       </c>
     </row>
+    <row r="1737" customHeight="1" spans="1:3">
+      <c r="A1737" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B1737" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1737" s="2">
+        <v>402581</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1735">
+  <autoFilter ref="A1:E1736">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1736</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1737</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -209,57 +209,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -274,23 +224,51 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -305,23 +283,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -329,6 +299,22 @@
     <font>
       <b/>
       <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -351,9 +337,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,61 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,55 +512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,19 +530,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,25 +548,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,15 +583,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -607,6 +598,35 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -618,30 +638,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -670,13 +666,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -839,14 +839,14 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
@@ -854,7 +854,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1737"/>
+  <dimension ref="A1:E1738"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23262,8 +23262,19 @@
         <v>402581</v>
       </c>
     </row>
+    <row r="1738" customHeight="1" spans="1:3">
+      <c r="A1738" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B1738" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1738" s="2">
+        <v>723695</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1736">
+  <autoFilter ref="A1:E1737">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1737</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1738</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,39 +208,33 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -252,23 +246,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -283,13 +262,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -305,19 +283,41 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -329,24 +329,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,25 +374,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,43 +404,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,13 +422,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,7 +458,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,25 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +530,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -554,7 +548,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,6 +583,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -594,15 +612,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -621,23 +630,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -657,26 +666,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,23 +838,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1738"/>
+  <dimension ref="A1:E1739"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23273,8 +23273,19 @@
         <v>723695</v>
       </c>
     </row>
+    <row r="1739" customHeight="1" spans="1:3">
+      <c r="A1739" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B1739" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1739" s="2">
+        <v>644418</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1737">
+  <autoFilter ref="A1:E1738">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1738</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1739</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1786" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -209,7 +209,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -217,30 +217,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -261,15 +245,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -283,39 +283,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -330,7 +307,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -338,7 +330,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -347,6 +339,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +386,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,31 +410,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,25 +422,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,7 +452,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,55 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,13 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,24 +583,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -618,35 +600,24 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -667,16 +638,45 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,9 +838,9 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
@@ -849,10 +849,10 @@
     <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1739"/>
+  <dimension ref="A1:E1740"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23284,8 +23284,19 @@
         <v>644418</v>
       </c>
     </row>
+    <row r="1740" customHeight="1" spans="1:3">
+      <c r="A1740" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B1740" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1740" s="2">
+        <v>308581</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1738">
+  <autoFilter ref="A1:E1739">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1739</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1740</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1786" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
@@ -208,8 +208,15 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -217,7 +224,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -230,31 +237,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -262,7 +262,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -276,69 +276,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -353,7 +292,68 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +386,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +404,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +416,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,19 +482,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,19 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,13 +512,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,67 +548,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,6 +583,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -594,60 +603,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -680,6 +635,51 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -839,14 +839,14 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
@@ -854,7 +854,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1740"/>
+  <dimension ref="A1:E1741"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23295,8 +23295,19 @@
         <v>308581</v>
       </c>
     </row>
+    <row r="1741" customHeight="1" spans="1:3">
+      <c r="A1741" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B1741" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1741" s="2">
+        <v>434438</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1739">
+  <autoFilter ref="A1:E1740">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1740</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1741</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -209,14 +209,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -231,38 +238,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -275,45 +258,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -328,17 +281,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -354,6 +314,46 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +392,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,61 +530,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,97 +548,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -587,7 +587,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -618,35 +633,24 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -666,17 +670,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,23 +838,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1741"/>
+  <dimension ref="A1:E1742"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23306,8 +23306,19 @@
         <v>434438</v>
       </c>
     </row>
+    <row r="1742" customHeight="1" spans="1:3">
+      <c r="A1742" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B1742" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1742" s="2">
+        <v>530950</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1740">
+  <autoFilter ref="A1:E1741">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1741</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1742</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -209,31 +209,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -244,45 +222,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -296,9 +238,61 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -320,6 +314,21 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -343,17 +352,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,13 +374,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,19 +422,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,61 +446,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,61 +458,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -554,7 +488,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -579,15 +579,6 @@
       </top>
       <bottom style="thin">
         <color indexed="22"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -625,16 +616,18 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -655,6 +648,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -669,17 +680,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,23 +838,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1742"/>
+  <dimension ref="A1:E1743"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23317,8 +23317,19 @@
         <v>530950</v>
       </c>
     </row>
+    <row r="1743" customHeight="1" spans="1:3">
+      <c r="A1743" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B1743" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1743" s="2">
+        <v>400907</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1741">
+  <autoFilter ref="A1:E1742">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1742</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1743</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -209,9 +209,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -222,9 +222,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -252,14 +282,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -273,6 +295,21 @@
       <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -291,8 +328,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -307,7 +345,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,44 +356,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,31 +374,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,79 +416,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,7 +440,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,7 +494,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,7 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,19 +530,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -579,21 +579,6 @@
       </top>
       <bottom style="thin">
         <color indexed="22"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,6 +618,36 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -651,8 +666,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,23 +675,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,23 +838,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1743"/>
+  <dimension ref="A1:E1744"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23328,8 +23328,19 @@
         <v>400907</v>
       </c>
     </row>
+    <row r="1744" customHeight="1" spans="1:3">
+      <c r="A1744" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B1744" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1744" s="2">
+        <v>453821</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1742">
+  <autoFilter ref="A1:E1743">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1743</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1744</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,121 +208,9 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -345,7 +233,104 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -356,6 +341,21 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,31 +374,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,43 +434,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,31 +458,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,19 +500,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,7 +518,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,19 +548,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,6 +583,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -598,36 +613,16 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -648,17 +643,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,6 +659,15 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,9 +838,9 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
@@ -849,10 +849,10 @@
     <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1744"/>
+  <dimension ref="A1:E1745"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23339,8 +23339,19 @@
         <v>453821</v>
       </c>
     </row>
+    <row r="1745" customHeight="1" spans="1:3">
+      <c r="A1745" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B1745" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1745" s="2">
+        <v>813295</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1743">
+  <autoFilter ref="A1:E1744">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1744</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1745</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
@@ -208,30 +208,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -240,9 +216,32 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -255,6 +254,36 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -262,14 +291,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -284,22 +306,15 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -313,34 +328,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -352,8 +351,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,13 +374,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,37 +470,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,115 +548,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,21 +583,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -613,17 +598,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,11 +633,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -672,11 +657,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -839,14 +839,14 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
@@ -854,7 +854,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1745"/>
+  <dimension ref="A1:E1746"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23350,8 +23350,19 @@
         <v>813295</v>
       </c>
     </row>
+    <row r="1746" customHeight="1" spans="1:3">
+      <c r="A1746" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B1746" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1746" s="2">
+        <v>804802</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1744">
+  <autoFilter ref="A1:E1745">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1745</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1746</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
@@ -222,16 +222,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -245,6 +237,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -253,8 +268,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -269,7 +308,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -284,7 +323,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -299,61 +353,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +410,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,19 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,49 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,73 +548,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,6 +583,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -594,15 +603,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,26 +633,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -675,8 +660,23 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -839,14 +839,14 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
@@ -854,7 +854,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1746"/>
+  <dimension ref="A1:E1747"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23361,8 +23361,19 @@
         <v>804802</v>
       </c>
     </row>
+    <row r="1747" customHeight="1" spans="1:3">
+      <c r="A1747" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B1747" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1747" s="2">
+        <v>601550</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1745">
+  <autoFilter ref="A1:E1746">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1746</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1747</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -208,6 +208,21 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -223,38 +238,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -270,9 +261,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -281,36 +272,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -323,7 +284,22 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -344,8 +320,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,13 +374,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +398,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,67 +428,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,25 +452,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,7 +470,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,19 +518,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,13 +542,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,15 +583,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -607,6 +598,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -618,17 +627,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -659,9 +657,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1747"/>
+  <dimension ref="A1:E1748"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23372,8 +23372,19 @@
         <v>601550</v>
       </c>
     </row>
+    <row r="1748" customHeight="1" spans="1:3">
+      <c r="A1748" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B1748" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1748" s="2">
+        <v>601550</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1746">
+  <autoFilter ref="A1:E1747">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1747</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1748</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,16 +208,37 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -230,8 +251,41 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -245,46 +299,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -305,33 +327,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -374,7 +374,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +386,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,31 +416,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,37 +434,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,31 +464,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,13 +494,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,7 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,7 +548,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,6 +583,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -594,15 +603,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -631,15 +631,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -651,6 +642,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,145 +688,145 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -838,23 +838,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1748"/>
+  <dimension ref="A1:E1749"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23383,8 +23383,19 @@
         <v>601550</v>
       </c>
     </row>
+    <row r="1749" customHeight="1" spans="1:3">
+      <c r="A1749" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B1749" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1749" s="2">
+        <v>365098</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1747">
+  <autoFilter ref="A1:E1748">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1748</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1749</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -208,37 +208,9 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -259,24 +231,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -292,7 +263,51 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -305,8 +320,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -319,11 +335,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -338,22 +354,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +428,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +446,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,55 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,79 +548,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -585,9 +585,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -611,7 +613,31 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -631,41 +657,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -680,6 +671,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1749"/>
+  <dimension ref="A1:E1750"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23394,8 +23394,19 @@
         <v>365098</v>
       </c>
     </row>
+    <row r="1750" customHeight="1" spans="1:3">
+      <c r="A1750" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B1750" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1750" s="2">
+        <v>407647</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1748">
+  <autoFilter ref="A1:E1749">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1749</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1750</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,9 +208,24 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -223,9 +238,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,6 +247,74 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -247,18 +329,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -266,80 +340,6 @@
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -352,10 +352,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,7 +374,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,37 +386,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,85 +416,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,7 +440,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,25 +530,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,17 +583,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -609,20 +598,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -642,17 +628,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -675,8 +666,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -839,14 +839,14 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
@@ -854,7 +854,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1750"/>
+  <dimension ref="A1:E1751"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23405,8 +23405,19 @@
         <v>407647</v>
       </c>
     </row>
+    <row r="1751" customHeight="1" spans="1:3">
+      <c r="A1751" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B1751" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1751" s="2">
+        <v>312884</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1749">
+  <autoFilter ref="A1:E1750">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1750</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1751</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -209,7 +209,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -217,17 +217,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -239,7 +231,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -260,24 +267,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -290,41 +297,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -343,6 +320,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -352,10 +352,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,13 +374,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,19 +386,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,19 +410,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,25 +428,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,7 +446,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,7 +476,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,7 +488,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,37 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,17 +583,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -614,16 +617,25 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -639,11 +651,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -662,24 +680,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,9 +838,9 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
@@ -849,10 +849,10 @@
     <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1751"/>
+  <dimension ref="A1:E1752"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23416,8 +23416,19 @@
         <v>312884</v>
       </c>
     </row>
+    <row r="1752" customHeight="1" spans="1:3">
+      <c r="A1752" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B1752" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1752" s="2">
+        <v>467419</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1750">
+  <autoFilter ref="A1:E1751">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1751</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1753</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -209,17 +209,16 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -230,8 +229,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -252,24 +252,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -284,7 +269,31 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -294,6 +303,28 @@
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -313,8 +344,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -322,38 +354,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,25 +374,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,13 +452,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,7 +488,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,7 +506,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,55 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -555,6 +543,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,11 +583,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -596,6 +602,17 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -631,26 +648,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -666,17 +663,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,16 +688,16 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -706,130 +706,130 @@
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,9 +838,9 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
@@ -849,10 +849,10 @@
     <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1752"/>
+  <dimension ref="A1:E1754"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23427,8 +23427,30 @@
         <v>467419</v>
       </c>
     </row>
+    <row r="1753" customHeight="1" spans="1:3">
+      <c r="A1753" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B1753" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1753" s="2">
+        <v>467419</v>
+      </c>
+    </row>
+    <row r="1754" customHeight="1" spans="1:3">
+      <c r="A1754" s="1">
+        <v>46312</v>
+      </c>
+      <c r="B1754" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1754" s="2">
+        <v>684933</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1751">
+  <autoFilter ref="A1:E1753">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1753</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1754</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -209,14 +209,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -231,14 +247,45 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -246,15 +293,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -269,31 +322,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -306,17 +335,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -330,30 +353,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +494,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,133 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,7 +548,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -607,32 +607,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -663,6 +637,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -680,6 +669,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,23 +838,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1754"/>
+  <dimension ref="A1:E1755"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23449,8 +23449,19 @@
         <v>684933</v>
       </c>
     </row>
+    <row r="1755" customHeight="1" spans="1:3">
+      <c r="A1755" s="1">
+        <v>46313</v>
+      </c>
+      <c r="B1755" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1755" s="2">
+        <v>698981</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1753">
+  <autoFilter ref="A1:E1754">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1754</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1755</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -209,15 +209,89 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -238,24 +312,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -270,57 +329,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -328,32 +351,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,49 +464,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +476,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,109 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,21 +583,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -622,17 +607,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -652,20 +631,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -680,6 +656,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,23 +838,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1755"/>
+  <dimension ref="A1:E1756"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23460,8 +23460,19 @@
         <v>698981</v>
       </c>
     </row>
+    <row r="1756" customHeight="1" spans="1:3">
+      <c r="A1756" s="1">
+        <v>46314</v>
+      </c>
+      <c r="B1756" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1756" s="2">
+        <v>398471</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1754">
+  <autoFilter ref="A1:E1755">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1755</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1756</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
@@ -208,15 +208,8 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -230,25 +223,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -262,29 +246,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -298,23 +277,15 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -329,23 +300,44 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -356,6 +348,14 @@
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,7 +374,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,19 +392,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,19 +428,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,13 +452,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,7 +476,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,13 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,7 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,55 +542,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,15 +583,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -609,9 +600,35 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -631,28 +648,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -671,15 +680,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -839,14 +839,14 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
@@ -854,7 +854,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1756"/>
+  <dimension ref="A1:E1757"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23471,8 +23471,19 @@
         <v>398471</v>
       </c>
     </row>
+    <row r="1757" customHeight="1" spans="1:3">
+      <c r="A1757" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B1757" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1757" s="2">
+        <v>517550</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1755">
+  <autoFilter ref="A1:E1756">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1756</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1757</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -210,6 +210,21 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -224,7 +239,36 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -232,23 +276,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,44 +291,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -313,8 +312,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -329,13 +337,14 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -343,19 +352,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,13 +374,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,73 +404,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,7 +422,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,7 +452,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,7 +500,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,49 +542,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -584,6 +584,30 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -594,6 +618,45 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -613,70 +676,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,9 +838,9 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
@@ -849,10 +849,10 @@
     <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1757"/>
+  <dimension ref="A1:E1758"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23482,8 +23482,19 @@
         <v>517550</v>
       </c>
     </row>
+    <row r="1758" customHeight="1" spans="1:3">
+      <c r="A1758" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1758" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1758" s="2">
+        <v>409035</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1756">
+  <autoFilter ref="A1:E1757">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1757</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1758</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,16 +208,15 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,21 +224,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -254,14 +239,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -274,11 +252,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -291,46 +284,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -345,6 +306,29 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -352,8 +336,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,19 +374,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,12 +422,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -422,7 +434,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,37 +506,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,85 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -607,6 +607,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -626,7 +637,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -646,37 +672,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,23 +838,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1758"/>
+  <dimension ref="A1:E1759"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23493,8 +23493,19 @@
         <v>409035</v>
       </c>
     </row>
+    <row r="1759" customHeight="1" spans="1:3">
+      <c r="A1759" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1759" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1759" s="2">
+        <v>369168</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1757">
+  <autoFilter ref="A1:E1758">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1758</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1759</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -208,76 +208,31 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -298,10 +253,10 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -314,7 +269,52 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -322,22 +322,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -352,8 +336,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,19 +434,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,103 +488,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,13 +500,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,19 +524,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,16 +583,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -601,18 +601,7 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -636,23 +625,32 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,9 +672,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,23 +838,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1759"/>
+  <dimension ref="A1:E1760"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23504,8 +23504,19 @@
         <v>369168</v>
       </c>
     </row>
+    <row r="1760" customHeight="1" spans="1:3">
+      <c r="A1760" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1760" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1760" s="2">
+        <v>547067</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1758">
+  <autoFilter ref="A1:E1759">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1759</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1761</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,9 +164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -208,24 +208,8 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -235,20 +219,6 @@
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -268,31 +238,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -313,8 +283,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -328,9 +321,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -339,14 +347,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,43 +452,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,55 +464,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,13 +488,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,7 +500,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,13 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,13 +530,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,17 +583,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -608,16 +608,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -655,17 +655,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -839,14 +839,14 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
@@ -854,7 +854,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1760"/>
+  <dimension ref="A1:E1762"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23515,8 +23515,30 @@
         <v>547067</v>
       </c>
     </row>
+    <row r="1761" customHeight="1" spans="1:3">
+      <c r="A1761" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1761" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1761" s="2">
+        <v>547067</v>
+      </c>
+    </row>
+    <row r="1762" customHeight="1" spans="1:3">
+      <c r="A1762" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B1762" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1762" s="2">
+        <v>789792</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1759">
+  <autoFilter ref="A1:E1761">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1761</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1762</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -211,12 +211,20 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -224,14 +232,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -246,16 +246,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -269,45 +284,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -315,22 +299,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -346,7 +315,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -356,6 +333,29 @@
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,37 +374,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,7 +398,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,7 +434,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,31 +446,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,79 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,17 +583,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -603,21 +597,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -646,11 +625,43 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -669,17 +680,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,9 +838,9 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
@@ -849,10 +849,10 @@
     <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1762"/>
+  <dimension ref="A1:E1763"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23537,8 +23537,19 @@
         <v>789792</v>
       </c>
     </row>
+    <row r="1763" customHeight="1" spans="1:3">
+      <c r="A1763" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B1763" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1763" s="2">
+        <v>637814</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1761">
+  <autoFilter ref="A1:E1762">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1762</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1763</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -215,37 +215,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -255,15 +224,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -276,8 +259,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -298,8 +282,46 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -314,6 +336,14 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -321,41 +351,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,31 +374,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,6 +416,102 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -428,37 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,7 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,79 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,11 +583,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -604,8 +619,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -640,17 +655,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -665,21 +680,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,23 +838,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1763"/>
+  <dimension ref="A1:E1764"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23548,8 +23548,19 @@
         <v>637814</v>
       </c>
     </row>
+    <row r="1764" customHeight="1" spans="1:3">
+      <c r="A1764" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1764" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1764" s="2">
+        <v>290660</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1762">
+  <autoFilter ref="A1:E1763">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1763</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1764</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -166,8 +166,8 @@
   <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
@@ -209,7 +209,120 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -224,112 +337,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -345,15 +353,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,25 +386,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,43 +428,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,25 +446,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,37 +518,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,19 +542,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,6 +583,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -594,6 +605,45 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -616,15 +666,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -639,47 +680,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1764"/>
+  <dimension ref="A1:E1765"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23559,8 +23559,19 @@
         <v>290660</v>
       </c>
     </row>
+    <row r="1765" customHeight="1" spans="1:3">
+      <c r="A1765" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1765" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1765" s="2">
+        <v>378903</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1763">
+  <autoFilter ref="A1:E1764">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1764</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1765</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,9 +165,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
@@ -209,7 +209,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -217,6 +232,66 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -231,45 +306,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -277,36 +321,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -321,23 +336,16 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -348,14 +356,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,7 +374,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,19 +416,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +434,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,7 +476,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,121 +542,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,13 +583,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -609,17 +637,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,35 +657,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -839,14 +839,14 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
@@ -854,7 +854,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1765"/>
+  <dimension ref="A1:E1766"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23570,8 +23570,19 @@
         <v>378903</v>
       </c>
     </row>
+    <row r="1766" customHeight="1" spans="1:3">
+      <c r="A1766" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1766" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1766" s="2">
+        <v>496880</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1764">
+  <autoFilter ref="A1:E1765">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1765</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1766</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="26">
@@ -209,82 +209,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -299,16 +224,16 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -320,24 +245,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -351,11 +290,72 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -374,66 +374,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -446,7 +386,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,7 +452,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,91 +548,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,45 +583,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -639,11 +600,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -652,7 +611,37 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -680,6 +669,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -839,14 +839,14 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
@@ -854,7 +854,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1766"/>
+  <dimension ref="A1:E1767"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23581,8 +23581,19 @@
         <v>496880</v>
       </c>
     </row>
+    <row r="1767" customHeight="1" spans="1:3">
+      <c r="A1767" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1767" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1767" s="2">
+        <v>369779</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1765">
+  <autoFilter ref="A1:E1766">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dashboard/data/incoming/本店.xlsx
+++ b/dashboard/data/incoming/本店.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1766</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1767</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -209,7 +209,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -224,59 +238,29 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -298,23 +282,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -328,6 +298,29 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -336,8 +329,23 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -346,14 +354,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -374,7 +374,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +398,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +422,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +494,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,31 +506,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,85 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -554,7 +554,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -584,6 +584,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -598,20 +613,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -631,21 +643,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -655,17 +652,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,148 +688,148 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
@@ -838,23 +838,23 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="50" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="50" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="50" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -1563,7 +1563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1767"/>
+  <dimension ref="A1:E1768"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23592,8 +23592,19 @@
         <v>369779</v>
       </c>
     </row>
+    <row r="1768" customHeight="1" spans="1:3">
+      <c r="A1768" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1768" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1768" s="2">
+        <v>339843</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1766">
+  <autoFilter ref="A1:E1767">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
